--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008414815340366153</v>
       </c>
       <c r="C2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>23390033</v>
+        <v>4368482</v>
       </c>
       <c r="L2" t="n">
-        <v>13916371</v>
+        <v>2367067</v>
       </c>
       <c r="M2" t="n">
-        <v>3550072</v>
+        <v>564414</v>
       </c>
       <c r="N2" t="n">
-        <v>197377</v>
+        <v>18897</v>
       </c>
       <c r="O2" t="n">
-        <v>2098373</v>
+        <v>338487</v>
       </c>
       <c r="P2" t="n">
-        <v>832385</v>
+        <v>139772</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999936819076538</v>
+        <v>0.9999916553497314</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9211070537567139</v>
+        <v>0.8540982604026794</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8335144519805908</v>
+        <v>0.7108345627784729</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7926368117332458</v>
+        <v>0.6283708214759827</v>
       </c>
       <c r="U2" t="n">
-        <v>0.588528037071228</v>
+        <v>0.2891881465911865</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8371448516845703</v>
+        <v>0.6993316411972046</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8876680731773376</v>
+        <v>0.7884429097175598</v>
       </c>
       <c r="X2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31731900</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="AG2" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AH2" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AI2" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565883278846741</v>
+        <v>0.9563066959381104</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112817645072937</v>
+        <v>0.9114376902580261</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580537438392639</v>
+        <v>0.8578296899795532</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622784733772278</v>
+        <v>0.6616203784942627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019806981086731</v>
+        <v>0.9018417000770569</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002016582438865534</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>23390033</v>
+        <v>4368482</v>
       </c>
       <c r="E3" t="n">
-        <v>1897249</v>
+        <v>669455</v>
       </c>
       <c r="F3" t="n">
-        <v>26006</v>
+        <v>12133</v>
       </c>
       <c r="G3" t="n">
-        <v>3296</v>
+        <v>1137</v>
       </c>
       <c r="H3" t="n">
-        <v>1288</v>
+        <v>653</v>
       </c>
       <c r="I3" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>50347900</v>
+        <v>10069567</v>
       </c>
       <c r="K3" t="n">
-        <v>54758671</v>
+        <v>10617868</v>
       </c>
       <c r="L3" t="n">
-        <v>62900809</v>
+        <v>12162984</v>
       </c>
       <c r="M3" t="n">
-        <v>76480691</v>
+        <v>15147078</v>
       </c>
       <c r="N3" t="n">
-        <v>81495423</v>
+        <v>16280133</v>
       </c>
       <c r="O3" t="n">
-        <v>79124938</v>
+        <v>15760766</v>
       </c>
       <c r="P3" t="n">
-        <v>81008079</v>
+        <v>16185103</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9238510727882385</v>
+        <v>0.8647233247756958</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8485827445983887</v>
+        <v>0.719451367855072</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7600942850112915</v>
+        <v>0.6035751700401306</v>
       </c>
       <c r="U3" t="n">
-        <v>0.441974550485611</v>
+        <v>0.21133092045784</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8239085078239441</v>
+        <v>0.6640828251838684</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8611606955528259</v>
+        <v>0.722735583782196</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24245260</v>
+        <v>4837248</v>
       </c>
       <c r="Z3" t="n">
-        <v>995349</v>
+        <v>199108</v>
       </c>
       <c r="AA3" t="n">
-        <v>42884</v>
+        <v>8602</v>
       </c>
       <c r="AB3" t="n">
-        <v>34102</v>
+        <v>6851</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50348100</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>55661737</v>
+        <v>11143104</v>
       </c>
       <c r="AG3" t="n">
-        <v>64227600</v>
+        <v>12835014</v>
       </c>
       <c r="AH3" t="n">
-        <v>76746838</v>
+        <v>15348021</v>
       </c>
       <c r="AI3" t="n">
-        <v>81482703</v>
+        <v>16296339</v>
       </c>
       <c r="AJ3" t="n">
-        <v>79283607</v>
+        <v>15856274</v>
       </c>
       <c r="AK3" t="n">
-        <v>81047145</v>
+        <v>16209353</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576305150985718</v>
+        <v>0.957513689994812</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099767208099365</v>
+        <v>0.9098963737487793</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575676679611206</v>
+        <v>0.8572810888290405</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618276834487915</v>
+        <v>0.6612800359725952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016205072402954</v>
+        <v>0.9016276001930237</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03185715663591164</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1891678</v>
+        <v>707253</v>
       </c>
       <c r="E4" t="n">
-        <v>13916371</v>
+        <v>2367067</v>
       </c>
       <c r="F4" t="n">
-        <v>541032</v>
+        <v>193029</v>
       </c>
       <c r="G4" t="n">
-        <v>14252</v>
+        <v>5484</v>
       </c>
       <c r="H4" t="n">
-        <v>33544</v>
+        <v>15795</v>
       </c>
       <c r="I4" t="n">
-        <v>2666</v>
+        <v>1471</v>
       </c>
       <c r="J4" t="n">
-        <v>200</v>
+        <v>53</v>
       </c>
       <c r="K4" t="n">
-        <v>2003359</v>
+        <v>746248</v>
       </c>
       <c r="L4" t="n">
-        <v>2779646</v>
+        <v>962916</v>
       </c>
       <c r="M4" t="n">
-        <v>928741</v>
+        <v>333804</v>
       </c>
       <c r="N4" t="n">
-        <v>137997</v>
+        <v>46448</v>
       </c>
       <c r="O4" t="n">
-        <v>408210</v>
+        <v>145528</v>
       </c>
       <c r="P4" t="n">
-        <v>105336</v>
+        <v>37504</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999968409538269</v>
+        <v>0.9999958276748657</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9224770665168762</v>
+        <v>0.8593779802322388</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8409810662269592</v>
+        <v>0.7151169776916504</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7760245203971863</v>
+        <v>0.6157234907150269</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5048301815986633</v>
+        <v>0.2442040890455246</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8304738998413086</v>
+        <v>0.6812515258789062</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8742135167121887</v>
+        <v>0.7541607022285461</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1027338</v>
+        <v>206350</v>
       </c>
       <c r="Z4" t="n">
-        <v>14923204</v>
+        <v>2993650</v>
       </c>
       <c r="AA4" t="n">
-        <v>415378</v>
+        <v>83345</v>
       </c>
       <c r="AB4" t="n">
-        <v>27557</v>
+        <v>5539</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1100293</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1452855</v>
+        <v>290886</v>
       </c>
       <c r="AH4" t="n">
-        <v>662594</v>
+        <v>132861</v>
       </c>
       <c r="AI4" t="n">
-        <v>150717</v>
+        <v>30242</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249541</v>
+        <v>50020</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571090936660767</v>
+        <v>0.9569098353385925</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106287360191345</v>
+        <v>0.9106664061546326</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578105568885803</v>
+        <v>0.8575552701950073</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620529890060425</v>
+        <v>0.661450207233429</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018005132675171</v>
+        <v>0.9017346501350403</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>68149</v>
+        <v>25083</v>
       </c>
       <c r="E5" t="n">
-        <v>768422</v>
+        <v>250480</v>
       </c>
       <c r="F5" t="n">
-        <v>3550072</v>
+        <v>564414</v>
       </c>
       <c r="G5" t="n">
-        <v>54044</v>
+        <v>16080</v>
       </c>
       <c r="H5" t="n">
-        <v>215304</v>
+        <v>72011</v>
       </c>
       <c r="I5" t="n">
-        <v>14571</v>
+        <v>7047</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1927937</v>
+        <v>683402</v>
       </c>
       <c r="L5" t="n">
-        <v>2483174</v>
+        <v>923033</v>
       </c>
       <c r="M5" t="n">
-        <v>1120496</v>
+        <v>370704</v>
       </c>
       <c r="N5" t="n">
-        <v>249203</v>
+        <v>70522</v>
       </c>
       <c r="O5" t="n">
-        <v>448479</v>
+        <v>171219</v>
       </c>
       <c r="P5" t="n">
-        <v>134200</v>
+        <v>53621</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999975562095642</v>
+        <v>0.9999967813491821</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9521040916442871</v>
+        <v>0.9129111766815186</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9358817934989929</v>
+        <v>0.8851152062416077</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9750336408615112</v>
+        <v>0.957084059715271</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9952826499938965</v>
+        <v>0.9928746223449707</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9895627498626709</v>
+        <v>0.9807049632072449</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9970816969871521</v>
+        <v>0.9944490194320679</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40265</v>
+        <v>8089</v>
       </c>
       <c r="Z5" t="n">
-        <v>426214</v>
+        <v>85507</v>
       </c>
       <c r="AA5" t="n">
-        <v>4005328</v>
+        <v>801659</v>
       </c>
       <c r="AB5" t="n">
-        <v>49808</v>
+        <v>9991</v>
       </c>
       <c r="AC5" t="n">
-        <v>145788</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1072710</v>
+        <v>214636</v>
       </c>
       <c r="AG5" t="n">
-        <v>1476341</v>
+        <v>296450</v>
       </c>
       <c r="AH5" t="n">
-        <v>665240</v>
+        <v>133459</v>
       </c>
       <c r="AI5" t="n">
-        <v>151021</v>
+        <v>30288</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250558</v>
+        <v>50141</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735257625579834</v>
+        <v>0.9734619855880737</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643129110336304</v>
+        <v>0.964221715927124</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838227033615112</v>
+        <v>0.9837768077850342</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963238835334778</v>
+        <v>0.9963127374649048</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939071536064148</v>
+        <v>0.9938985705375671</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383641242981</v>
+        <v>0.9983823895454407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>43054</v>
+        <v>13574</v>
       </c>
       <c r="E6" t="n">
-        <v>70051</v>
+        <v>19399</v>
       </c>
       <c r="F6" t="n">
-        <v>94358</v>
+        <v>25329</v>
       </c>
       <c r="G6" t="n">
-        <v>197377</v>
+        <v>18897</v>
       </c>
       <c r="H6" t="n">
-        <v>38340</v>
+        <v>11017</v>
       </c>
       <c r="I6" t="n">
-        <v>3337</v>
+        <v>1176</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32411</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>26831</v>
+        <v>5380</v>
       </c>
       <c r="AA6" t="n">
-        <v>54451</v>
+        <v>10917</v>
       </c>
       <c r="AB6" t="n">
-        <v>295559</v>
+        <v>59131</v>
       </c>
       <c r="AC6" t="n">
-        <v>34923</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>381</v>
+        <v>309</v>
       </c>
       <c r="E7" t="n">
-        <v>41849</v>
+        <v>22452</v>
       </c>
       <c r="F7" t="n">
-        <v>258469</v>
+        <v>98573</v>
       </c>
       <c r="G7" t="n">
-        <v>63092</v>
+        <v>22094</v>
       </c>
       <c r="H7" t="n">
-        <v>2098373</v>
+        <v>338487</v>
       </c>
       <c r="I7" t="n">
-        <v>84671</v>
+        <v>27790</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4056</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148230</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37923</v>
+        <v>7595</v>
       </c>
       <c r="AC7" t="n">
-        <v>2296294</v>
+        <v>459565</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>2075</v>
+        <v>1130</v>
       </c>
       <c r="F8" t="n">
-        <v>8876</v>
+        <v>4740</v>
       </c>
       <c r="G8" t="n">
-        <v>3313</v>
+        <v>1653</v>
       </c>
       <c r="H8" t="n">
-        <v>119734</v>
+        <v>46052</v>
       </c>
       <c r="I8" t="n">
-        <v>832385</v>
+        <v>139772</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
